--- a/test/fixtures/products-import-invalid.xlsx
+++ b/test/fixtures/products-import-invalid.xlsx
@@ -34,6 +34,9 @@
     <t>category</t>
   </si>
   <si>
+    <t>subcategory</t>
+  </si>
+  <si>
     <t>rating</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>KITCHEN</t>
   </si>
   <si>
+    <t>APPLIANCES</t>
+  </si>
+  <si>
     <t>Row without a name</t>
   </si>
   <si>
@@ -74,6 +80,18 @@
   </si>
   <si>
     <t>SPORTS</t>
+  </si>
+  <si>
+    <t>FITNESS</t>
+  </si>
+  <si>
+    <t>Import No Subcategory</t>
+  </si>
+  <si>
+    <t>Import Lamp In Kitchen</t>
+  </si>
+  <si>
+    <t>LIGHTING</t>
   </si>
 </sst>
 </file>
@@ -138,113 +156,171 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2">
         <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>-1</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
